--- a/sport_profile_database_v1_5.xlsx
+++ b/sport_profile_database_v1_5.xlsx
@@ -28051,7 +28051,7 @@
         <v>5</v>
       </c>
       <c r="N98" s="70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O98" s="70" t="n">
         <v>5</v>
@@ -28176,7 +28176,7 @@
         <v>5</v>
       </c>
       <c r="N99" s="70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O99" s="70" t="n">
         <v>4</v>
@@ -29947,5796 +29947,5796 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="36" t="inlineStr">
         <is>
           <t>SP66</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="36" t="inlineStr">
         <is>
           <t>Golf</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="36" t="inlineStr">
         <is>
           <t>Competitive (all)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="36" t="n">
         <v>183</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="36" t="n">
         <v>87</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="M114" t="n">
+      <c r="M114" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N114" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="O114" t="n">
+      <c r="O114" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P114" t="n">
+      <c r="P114" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="Q114" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="R114" t="n">
+      <c r="R114" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="S114" t="n">
+      <c r="S114" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T114" t="n">
+      <c r="T114" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U114" t="n">
+      <c r="U114" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V114" t="n">
+      <c r="V114" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W114" t="inlineStr">
+      <c r="W114" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="X114" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Y114" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
+      <c r="Z114" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA114" t="inlineStr">
+      <c r="AA114" s="36" t="inlineStr">
         <is>
           <t>8–16</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
+      <c r="AB114" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC114" t="n">
+      <c r="AC114" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="AD114" t="inlineStr">
+      <c r="AD114" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE114" t="inlineStr">
+      <c r="AE114" s="36" t="inlineStr">
         <is>
           <t>PGA Tour, European Tour</t>
         </is>
       </c>
-      <c r="AF114" t="inlineStr">
+      <c r="AF114" s="36" t="inlineStr">
         <is>
           <t>PGA Tour player composite; rotational power through the kinetic chain is the primary physical determinant, not brute strength.</t>
         </is>
       </c>
-      <c r="AG114" t="inlineStr">
+      <c r="AG114" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="36" t="inlineStr">
         <is>
           <t>SP67</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="36" t="inlineStr">
         <is>
           <t>Equestrian</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="36" t="inlineStr">
         <is>
           <t>Show jumping (male/mixed)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="36" t="n">
         <v>170</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115" s="36" t="n">
         <v>64</v>
       </c>
-      <c r="H115" t="n">
+      <c r="H115" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I115" t="n">
+      <c r="I115" s="36" t="n">
         <v>22.1</v>
       </c>
-      <c r="J115" t="n">
+      <c r="J115" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="M115" t="n">
+      <c r="M115" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N115" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="O115" t="n">
+      <c r="O115" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P115" t="n">
+      <c r="P115" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="Q115" t="n">
+      <c r="Q115" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="R115" t="n">
+      <c r="R115" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="S115" t="n">
+      <c r="S115" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T115" t="n">
+      <c r="T115" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U115" t="n">
+      <c r="U115" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V115" t="n">
+      <c r="V115" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W115" t="inlineStr">
+      <c r="W115" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="X115" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Y115" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
+      <c r="Z115" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA115" t="inlineStr">
+      <c r="AA115" s="36" t="inlineStr">
         <is>
           <t>6–14</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
+      <c r="AB115" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC115" t="n">
+      <c r="AC115" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD115" t="inlineStr">
+      <c r="AD115" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE115" t="inlineStr">
+      <c r="AE115" s="36" t="inlineStr">
         <is>
           <t>FEI World ranking athlete data</t>
         </is>
       </c>
-      <c r="AF115" t="inlineStr">
+      <c r="AF115" s="36" t="inlineStr">
         <is>
           <t>Elite show jumping riders average ~170 cm / 64 kg; lighter riders preferred for horse performance. High injury risk from falls despite no opponent contact.</t>
         </is>
       </c>
-      <c r="AG115" t="inlineStr">
+      <c r="AG115" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="36" t="inlineStr">
         <is>
           <t>SP68</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="36" t="inlineStr">
         <is>
           <t>Cricket</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="36" t="inlineStr">
         <is>
           <t>All-rounder (male)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="36" t="inlineStr">
         <is>
           <t>Team field</t>
         </is>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="36" t="n">
         <v>180</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116" s="36" t="n">
         <v>79</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H116" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I116" t="n">
+      <c r="I116" s="36" t="n">
         <v>24.4</v>
       </c>
-      <c r="J116" t="n">
+      <c r="J116" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="M116" t="n">
+      <c r="M116" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N116" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O116" t="n">
+      <c r="O116" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P116" t="n">
+      <c r="P116" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q116" t="n">
+      <c r="Q116" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R116" t="n">
+      <c r="R116" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S116" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T116" t="n">
+      <c r="T116" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U116" t="n">
+      <c r="U116" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V116" t="n">
+      <c r="V116" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="W116" t="inlineStr">
+      <c r="W116" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="X116" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Y116" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
+      <c r="Z116" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA116" t="inlineStr">
+      <c r="AA116" s="36" t="inlineStr">
         <is>
           <t>8–14</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
+      <c r="AB116" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC116" t="n">
+      <c r="AC116" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD116" t="inlineStr">
+      <c r="AD116" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE116" t="inlineStr">
+      <c r="AE116" s="36" t="inlineStr">
         <is>
           <t>ICC international player database</t>
         </is>
       </c>
-      <c r="AF116" t="inlineStr">
+      <c r="AF116" s="36" t="inlineStr">
         <is>
           <t>International cricketer composite all-rounder profile. Fast bowlers typically taller/heavier; batters and spinners lean lighter.</t>
         </is>
       </c>
-      <c r="AG116" t="inlineStr">
+      <c r="AG116" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="36" t="inlineStr">
         <is>
           <t>SP69</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="36" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="36" t="inlineStr">
         <is>
           <t>Recurve / compound (male)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117" s="36" t="n">
         <v>74</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H117" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="I117" t="n">
+      <c r="I117" s="36" t="n">
         <v>24.2</v>
       </c>
-      <c r="J117" t="n">
+      <c r="J117" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="M117" t="n">
+      <c r="M117" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="N117" t="n">
+      <c r="N117" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="O117" t="n">
+      <c r="O117" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P117" t="n">
+      <c r="P117" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="Q117" t="n">
+      <c r="Q117" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R117" t="n">
+      <c r="R117" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S117" t="n">
+      <c r="S117" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T117" t="n">
+      <c r="T117" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U117" t="n">
+      <c r="U117" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="V117" t="n">
+      <c r="V117" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W117" t="inlineStr">
+      <c r="W117" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="X117" s="36" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Y117" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
+      <c r="Z117" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA117" t="inlineStr">
+      <c r="AA117" s="36" t="inlineStr">
         <is>
           <t>10–16</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
+      <c r="AB117" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC117" t="n">
+      <c r="AC117" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="AD117" t="inlineStr">
+      <c r="AD117" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE117" t="inlineStr">
+      <c r="AE117" s="36" t="inlineStr">
         <is>
           <t>World Archery athlete profiles</t>
         </is>
       </c>
-      <c r="AF117" t="inlineStr">
+      <c r="AF117" s="36" t="inlineStr">
         <is>
           <t>Physical profile is broad — technique, mental focus, and draw-side upper body endurance dominate over body type.</t>
         </is>
       </c>
-      <c r="AG117" t="inlineStr">
+      <c r="AG117" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="36" t="inlineStr">
         <is>
           <t>SP70</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="36" t="inlineStr">
         <is>
           <t>Sport shooting</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="36" t="inlineStr">
         <is>
           <t>Pistol / rifle (male)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118" s="36" t="n">
         <v>78</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H118" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="I118" t="n">
+      <c r="I118" s="36" t="n">
         <v>25.5</v>
       </c>
-      <c r="J118" t="n">
+      <c r="J118" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M118" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N118" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="O118" t="n">
+      <c r="O118" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="P118" t="n">
+      <c r="P118" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q118" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R118" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S118" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="T118" t="n">
+      <c r="T118" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U118" t="n">
+      <c r="U118" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V118" t="n">
+      <c r="V118" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W118" t="inlineStr">
+      <c r="W118" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="X118" s="36" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Y118" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
+      <c r="Z118" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA118" t="inlineStr">
+      <c r="AA118" s="36" t="inlineStr">
         <is>
           <t>14–25</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
+      <c r="AB118" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC118" t="n">
+      <c r="AC118" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="AD118" t="inlineStr">
+      <c r="AD118" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE118" t="inlineStr">
+      <c r="AE118" s="36" t="inlineStr">
         <is>
           <t>ISSF World Cup athlete profiles</t>
         </is>
       </c>
-      <c r="AF118" t="inlineStr">
+      <c r="AF118" s="36" t="inlineStr">
         <is>
           <t>Almost no physical filter — sport is decided by fine motor control, breath control, and mental composure under pressure.</t>
         </is>
       </c>
-      <c r="AG118" t="inlineStr">
+      <c r="AG118" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="36" t="inlineStr">
         <is>
           <t>SP71</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="36" t="inlineStr">
         <is>
           <t>Darts</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="36" t="inlineStr">
         <is>
           <t>Professional (male)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G119" s="36" t="n">
         <v>82</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H119" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="I119" t="n">
+      <c r="I119" s="36" t="n">
         <v>26.8</v>
       </c>
-      <c r="J119" t="n">
+      <c r="J119" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="M119" t="n">
+      <c r="M119" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="N119" t="n">
+      <c r="N119" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="O119" t="n">
+      <c r="O119" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="P119" t="n">
+      <c r="P119" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
+      <c r="Q119" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R119" t="n">
+      <c r="R119" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="S119" t="n">
+      <c r="S119" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="T119" t="n">
+      <c r="T119" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U119" t="n">
+      <c r="U119" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V119" t="n">
+      <c r="V119" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W119" t="inlineStr">
+      <c r="W119" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="X119" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Y119" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
+      <c r="Z119" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA119" t="inlineStr">
+      <c r="AA119" s="36" t="inlineStr">
         <is>
           <t>14–30</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
+      <c r="AB119" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC119" t="n">
+      <c r="AC119" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD119" t="inlineStr">
+      <c r="AD119" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE119" t="inlineStr">
+      <c r="AE119" s="36" t="inlineStr">
         <is>
           <t>PDC player statistics</t>
         </is>
       </c>
-      <c r="AF119" t="inlineStr">
+      <c r="AF119" s="36" t="inlineStr">
         <is>
           <t>Physical profile is near-irrelevant; fine motor precision, mental arithmetic, and composure under crowd pressure determine elite performance.</t>
         </is>
       </c>
-      <c r="AG119" t="inlineStr">
+      <c r="AG119" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="36" t="inlineStr">
         <is>
           <t>SP72</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="36" t="inlineStr">
         <is>
           <t>Lawn bowls</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="36" t="inlineStr">
         <is>
           <t>Competitive (male)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="36" t="inlineStr">
         <is>
           <t>Team precision</t>
         </is>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="I120" t="n">
+      <c r="I120" s="36" t="n">
         <v>26.1</v>
       </c>
-      <c r="J120" t="n">
+      <c r="J120" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="M120" t="n">
+      <c r="M120" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="N120" t="n">
+      <c r="N120" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="O120" t="n">
+      <c r="O120" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="P120" t="n">
+      <c r="P120" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="Q120" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R120" t="n">
+      <c r="R120" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S120" t="n">
+      <c r="S120" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T120" t="n">
+      <c r="T120" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U120" t="n">
+      <c r="U120" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="V120" t="n">
+      <c r="V120" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="W120" t="inlineStr">
+      <c r="W120" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="X120" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Y120" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
+      <c r="Z120" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA120" t="inlineStr">
+      <c r="AA120" s="36" t="inlineStr">
         <is>
           <t>16+</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
+      <c r="AB120" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC120" t="n">
+      <c r="AC120" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD120" t="inlineStr">
+      <c r="AD120" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE120" t="inlineStr">
+      <c r="AE120" s="36" t="inlineStr">
         <is>
           <t>Bowls Ireland club data</t>
         </is>
       </c>
-      <c r="AF120" t="inlineStr">
+      <c r="AF120" s="36" t="inlineStr">
         <is>
           <t>Very broad physical profile; tactical reading of the head and fine motor precision are the primary performance drivers. Accessible late-start sport.</t>
         </is>
       </c>
-      <c r="AG120" t="inlineStr">
+      <c r="AG120" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="36" t="inlineStr">
         <is>
           <t>SP73</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="36" t="inlineStr">
         <is>
           <t>Gymnastics (Artistic)</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="36" t="inlineStr">
         <is>
           <t>Male senior elite</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="36" t="inlineStr">
         <is>
           <t>Individual aesthetic</t>
         </is>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="36" t="n">
         <v>167</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H121" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I121" t="n">
+      <c r="I121" s="36" t="n">
         <v>24.7</v>
       </c>
-      <c r="J121" t="n">
+      <c r="J121" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="M121" t="n">
+      <c r="M121" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N121" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O121" t="n">
+      <c r="O121" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P121" t="n">
+      <c r="P121" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q121" t="n">
+      <c r="Q121" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="R121" t="n">
+      <c r="R121" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S121" t="n">
+      <c r="S121" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="T121" t="n">
+      <c r="T121" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="U121" t="n">
+      <c r="U121" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V121" t="n">
+      <c r="V121" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W121" t="inlineStr">
+      <c r="W121" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="X121" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Y121" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
+      <c r="Z121" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA121" t="inlineStr">
+      <c r="AA121" s="36" t="inlineStr">
         <is>
           <t>4–8</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
+      <c r="AB121" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC121" t="n">
+      <c r="AC121" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="AD121" t="inlineStr">
+      <c r="AD121" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE121" t="inlineStr">
+      <c r="AE121" s="36" t="inlineStr">
         <is>
           <t>FIG World Championship athlete data</t>
         </is>
       </c>
-      <c r="AF121" t="inlineStr">
+      <c r="AF121" s="36" t="inlineStr">
         <is>
           <t>Elite male gymnasts are among the strongest athletes relative to bodyweight in any sport — rings, parallel bars, and floor require extraordinary absolute strength in a compact frame.</t>
         </is>
       </c>
-      <c r="AG121" t="inlineStr">
+      <c r="AG121" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="36" t="inlineStr">
         <is>
           <t>SP74</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="36" t="inlineStr">
         <is>
           <t>Karate</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="36" t="inlineStr">
         <is>
           <t>Kumite (male elite)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="36" t="inlineStr">
         <is>
           <t>Combat striking</t>
         </is>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122" s="36" t="n">
         <v>74</v>
       </c>
-      <c r="H122" t="n">
+      <c r="H122" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I122" t="n">
+      <c r="I122" s="36" t="n">
         <v>24.2</v>
       </c>
-      <c r="J122" t="n">
+      <c r="J122" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M122" t="n">
+      <c r="M122" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N122" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O122" t="n">
+      <c r="O122" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P122" t="n">
+      <c r="P122" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q122" t="n">
+      <c r="Q122" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R122" t="n">
+      <c r="R122" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S122" t="n">
+      <c r="S122" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T122" t="n">
+      <c r="T122" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U122" t="n">
+      <c r="U122" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V122" t="n">
+      <c r="V122" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="W122" s="36" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="X122" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Y122" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
+      <c r="Z122" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA122" t="inlineStr">
+      <c r="AA122" s="36" t="inlineStr">
         <is>
           <t>6–12</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
+      <c r="AB122" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC122" t="n">
+      <c r="AC122" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD122" t="inlineStr">
+      <c r="AD122" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE122" t="inlineStr">
+      <c r="AE122" s="36" t="inlineStr">
         <is>
           <t>WKF World Championship data</t>
         </is>
       </c>
-      <c r="AF122" t="inlineStr">
+      <c r="AF122" s="36" t="inlineStr">
         <is>
           <t>Olympic karate kumite elite composite; contact is controlled and point-scoring — lower injury risk than full-contact striking despite high intensity.</t>
         </is>
       </c>
-      <c r="AG122" t="inlineStr">
+      <c r="AG122" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="36" t="inlineStr">
         <is>
           <t>SP75</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="36" t="inlineStr">
         <is>
           <t>Muay Thai</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="36" t="inlineStr">
         <is>
           <t>Professional (light–welterweight)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="36" t="inlineStr">
         <is>
           <t>Combat striking</t>
         </is>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="36" t="n">
         <v>172</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G123" s="36" t="n">
         <v>68</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H123" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I123" t="n">
+      <c r="I123" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="J123" t="n">
+      <c r="J123" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M123" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N123" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O123" t="n">
+      <c r="O123" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P123" t="n">
+      <c r="P123" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="Q123" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="R123" t="n">
+      <c r="R123" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S123" t="n">
+      <c r="S123" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T123" t="n">
+      <c r="T123" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U123" t="n">
+      <c r="U123" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V123" t="n">
+      <c r="V123" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W123" t="inlineStr">
+      <c r="W123" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="X123" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Y123" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
+      <c r="Z123" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA123" t="inlineStr">
+      <c r="AA123" s="36" t="inlineStr">
         <is>
           <t>10–18</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
+      <c r="AB123" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC123" t="n">
+      <c r="AC123" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD123" t="inlineStr">
+      <c r="AD123" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE123" t="inlineStr">
+      <c r="AE123" s="36" t="inlineStr">
         <is>
           <t>WBC Muay Thai / ONE Championship athlete data</t>
         </is>
       </c>
-      <c r="AF123" t="inlineStr">
+      <c r="AF123" s="36" t="inlineStr">
         <is>
           <t>Professional Muay Thai composite at lighter weight classes; eight-limb striking demands the highest aerobic endurance of any striking art.</t>
         </is>
       </c>
-      <c r="AG123" t="inlineStr">
+      <c r="AG123" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="36" t="inlineStr">
         <is>
           <t>SP01F</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="36" t="inlineStr">
         <is>
           <t>Soccer (football)</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="36" t="inlineStr">
         <is>
           <t>Outfield (all)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="36" t="inlineStr">
         <is>
           <t>Team field</t>
         </is>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="36" t="n">
         <v>166</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G124" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H124" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I124" s="36" t="n">
         <v>21.8</v>
       </c>
-      <c r="J124" t="n">
+      <c r="J124" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="M124" t="n">
+      <c r="M124" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N124" t="n">
+      <c r="N124" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O124" t="n">
+      <c r="O124" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P124" t="n">
+      <c r="P124" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q124" t="n">
+      <c r="Q124" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R124" t="n">
+      <c r="R124" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="S124" t="n">
+      <c r="S124" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T124" t="n">
+      <c r="T124" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U124" t="n">
+      <c r="U124" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V124" t="n">
+      <c r="V124" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="W124" t="inlineStr">
+      <c r="W124" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="X124" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Y124" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="Z124" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AA124" s="36" t="inlineStr">
         <is>
           <t>5–8</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
+      <c r="AB124" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC124" t="n">
+      <c r="AC124" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="AD124" t="inlineStr">
+      <c r="AD124" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE124" t="inlineStr">
+      <c r="AE124" s="36" t="inlineStr">
         <is>
           <t>Datson N et al. (2017) J Strength Cond Res; Andersson H et al. (2010) Int J Sports Physiol Perform.</t>
         </is>
       </c>
-      <c r="AF124" t="inlineStr">
+      <c r="AF124" s="36" t="inlineStr">
         <is>
           <t>Elite female outfield players 165–167 cm / 58–63 kg (Datson et al. 2017 NWSL/WSL; Andersson et al. 2010 Champions League). Applied sex differentials for derivation.</t>
         </is>
       </c>
-      <c r="AG124" t="inlineStr">
+      <c r="AG124" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="36" t="inlineStr">
         <is>
           <t>SP02F</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="36" t="inlineStr">
         <is>
           <t>Basketball</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="36" t="inlineStr">
         <is>
           <t>All positions (NBA mean)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="36" t="inlineStr">
         <is>
           <t>Team court</t>
         </is>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="36" t="n">
         <v>183</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G125" s="36" t="n">
         <v>78</v>
       </c>
-      <c r="H125" t="n">
+      <c r="H125" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="I125" t="n">
+      <c r="I125" s="36" t="n">
         <v>23.3</v>
       </c>
-      <c r="J125" t="n">
+      <c r="J125" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="K125" t="n">
+      <c r="K125" s="36" t="n">
         <v>1.06</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M125" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N125" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O125" t="n">
+      <c r="O125" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P125" t="n">
+      <c r="P125" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="Q125" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R125" t="n">
+      <c r="R125" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S125" t="n">
+      <c r="S125" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T125" t="n">
+      <c r="T125" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U125" t="n">
+      <c r="U125" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V125" t="n">
+      <c r="V125" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="W125" t="inlineStr">
+      <c r="W125" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="X125" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Y125" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
+      <c r="Z125" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA125" t="inlineStr">
+      <c r="AA125" s="36" t="inlineStr">
         <is>
           <t>6–10</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
+      <c r="AB125" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC125" t="n">
+      <c r="AC125" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD125" t="inlineStr">
+      <c r="AD125" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE125" t="inlineStr">
+      <c r="AE125" s="36" t="inlineStr">
         <is>
           <t>Torres-Unda J et al. (2013) J Hum Kinet; WNBA Draft Combine data.</t>
         </is>
       </c>
-      <c r="AF125" t="inlineStr">
+      <c r="AF125" s="36" t="inlineStr">
         <is>
           <t>WNBA combine: mean 183 cm, 77–80 kg (Torres-Unda et al. 2013). Lighter than simple scaling predicts due to position spread.</t>
         </is>
       </c>
-      <c r="AG125" t="inlineStr">
+      <c r="AG125" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="36" t="inlineStr">
         <is>
           <t>SP04F</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="36" t="inlineStr">
         <is>
           <t>Road cycling</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="36" t="inlineStr">
         <is>
           <t>Grand Tour all-rounder</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="36" t="inlineStr">
         <is>
           <t>Endurance individual</t>
         </is>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="36" t="n">
         <v>169</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G126" s="36" t="n">
         <v>57</v>
       </c>
-      <c r="H126" t="n">
+      <c r="H126" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="I126" t="n">
+      <c r="I126" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="J126" t="n">
+      <c r="J126" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="M126" t="n">
+      <c r="M126" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="N126" t="n">
+      <c r="N126" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="O126" t="n">
+      <c r="O126" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P126" t="n">
+      <c r="P126" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q126" t="n">
+      <c r="Q126" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R126" t="n">
+      <c r="R126" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="S126" t="n">
+      <c r="S126" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="T126" t="n">
+      <c r="T126" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="U126" t="n">
+      <c r="U126" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V126" t="n">
+      <c r="V126" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W126" t="inlineStr">
+      <c r="W126" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="X126" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Y126" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
+      <c r="Z126" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA126" t="inlineStr">
+      <c r="AA126" s="36" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
+      <c r="AB126" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC126" t="n">
+      <c r="AC126" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD126" t="inlineStr">
+      <c r="AD126" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE126" t="inlineStr">
+      <c r="AE126" s="36" t="inlineStr">
         <is>
           <t>Lucia A et al. (2001) Med Sci Sports Exerc; UCI Women WorldTour physiological data.</t>
         </is>
       </c>
-      <c r="AF126" t="inlineStr">
+      <c r="AF126" s="36" t="inlineStr">
         <is>
           <t>UCI Women WorldTour athletes among leanest in sport; VO2max ~65 ml/kg/min. Lighter and shorter than simple scaling predicts.</t>
         </is>
       </c>
-      <c r="AG126" t="inlineStr">
+      <c r="AG126" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="36" t="inlineStr">
         <is>
           <t>SP06F</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="36" t="inlineStr">
         <is>
           <t>Rugby union</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="36" t="inlineStr">
         <is>
           <t>Forwards (female)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="36" t="inlineStr">
         <is>
           <t>Team field contact</t>
         </is>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="36" t="n">
         <v>170</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127" s="36" t="n">
         <v>72</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H127" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I127" t="n">
+      <c r="I127" s="36" t="n">
         <v>24.9</v>
       </c>
-      <c r="J127" t="n">
+      <c r="J127" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M127" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N127" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O127" t="n">
+      <c r="O127" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P127" t="n">
+      <c r="P127" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q127" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R127" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S127" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="T127" t="n">
+      <c r="T127" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="U127" t="n">
+      <c r="U127" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="V127" t="n">
+      <c r="V127" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="W127" t="inlineStr">
+      <c r="W127" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="X127" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Y127" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
+      <c r="Z127" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA127" t="inlineStr">
+      <c r="AA127" s="36" t="inlineStr">
         <is>
           <t>6–10</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
+      <c r="AB127" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC127" t="n">
+      <c r="AC127" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD127" t="inlineStr">
+      <c r="AD127" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE127" t="inlineStr">
+      <c r="AE127" s="36" t="inlineStr">
         <is>
           <t>World Rugby physical data; Hollander K et al. (2019) BMJ Open Sport Exerc Med.</t>
         </is>
       </c>
-      <c r="AF127" t="inlineStr">
+      <c r="AF127" s="36" t="inlineStr">
         <is>
           <t>World Rugby female forwards: 168–173 cm, 68–76 kg. Heavier build for contact demands. Strong growth in women's rugby in Ireland (Interprovincial + AIL Women).</t>
         </is>
       </c>
-      <c r="AG127" t="inlineStr">
+      <c r="AG127" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="36" t="inlineStr">
         <is>
           <t>SP09F</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="36" t="inlineStr">
         <is>
           <t>Tennis</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="36" t="inlineStr">
         <is>
           <t>Singles (WTA)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="36" t="inlineStr">
         <is>
           <t>Individual racquet</t>
         </is>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="36" t="n">
         <v>64</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I128" s="36" t="n">
         <v>20.9</v>
       </c>
-      <c r="J128" t="n">
+      <c r="J128" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="M128" t="n">
+      <c r="M128" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N128" t="n">
+      <c r="N128" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O128" t="n">
+      <c r="O128" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P128" t="n">
+      <c r="P128" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="Q128" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R128" t="n">
+      <c r="R128" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="S128" t="n">
+      <c r="S128" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T128" t="n">
+      <c r="T128" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U128" t="n">
+      <c r="U128" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V128" t="n">
+      <c r="V128" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W128" t="inlineStr">
+      <c r="W128" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="X128" s="36" t="inlineStr">
         <is>
           <t>Outdoor / indoor</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Y128" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="Z128" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA128" t="inlineStr">
+      <c r="AA128" s="36" t="inlineStr">
         <is>
           <t>5–8</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
+      <c r="AB128" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC128" t="n">
+      <c r="AC128" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD128" t="inlineStr">
+      <c r="AD128" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE128" t="inlineStr">
+      <c r="AE128" s="36" t="inlineStr">
         <is>
           <t>Pugh SF et al. (2022) Int J Sports Sci Coach; WTA official data.</t>
         </is>
       </c>
-      <c r="AF128" t="inlineStr">
+      <c r="AF128" s="36" t="inlineStr">
         <is>
           <t>WTA top-100 mean ~175 cm, 63–66 kg. Height advantage on serve increasingly pronounced. Pugh et al. (2022).</t>
         </is>
       </c>
-      <c r="AG128" t="inlineStr">
+      <c r="AG128" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="36" t="inlineStr">
         <is>
           <t>SP12F</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="36" t="inlineStr">
         <is>
           <t>Sport climbing</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="36" t="inlineStr">
         <is>
           <t>Lead / bouldering (female)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="36" t="n">
         <v>163</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G129" t="n">
+      <c r="G129" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="H129" t="n">
+      <c r="H129" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="I129" t="n">
+      <c r="I129" s="36" t="n">
         <v>19.2</v>
       </c>
-      <c r="J129" t="n">
+      <c r="J129" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="K129" t="n">
+      <c r="K129" s="36" t="n">
         <v>1.01</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M129" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N129" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O129" t="n">
+      <c r="O129" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="P129" t="n">
+      <c r="P129" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="Q129" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="R129" t="n">
+      <c r="R129" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S129" t="n">
+      <c r="S129" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="T129" t="n">
+      <c r="T129" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U129" t="n">
+      <c r="U129" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V129" t="n">
+      <c r="V129" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W129" t="inlineStr">
+      <c r="W129" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="X129" s="36" t="inlineStr">
         <is>
           <t>Indoor / outdoor</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Y129" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
+      <c r="Z129" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA129" t="inlineStr">
+      <c r="AA129" s="36" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
+      <c r="AB129" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC129" t="n">
+      <c r="AC129" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD129" t="inlineStr">
+      <c r="AD129" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE129" t="inlineStr">
+      <c r="AE129" s="36" t="inlineStr">
         <is>
           <t>Giles D et al. (2014) J Hum Kinet; Watts PB et al. (2003) J Sports Med Phys Fitness.</t>
         </is>
       </c>
-      <c r="AF129" t="inlineStr">
+      <c r="AF129" s="36" t="inlineStr">
         <is>
           <t>Elite female climbers: extremely lean, slight positive ape index. Giles et al. (2014) bouldering/lead cohort.</t>
         </is>
       </c>
-      <c r="AG129" t="inlineStr">
+      <c r="AG129" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="36" t="inlineStr">
         <is>
           <t>SP14F</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="36" t="inlineStr">
         <is>
           <t>MMA</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="36" t="inlineStr">
         <is>
           <t>All disciplines (strawweight–flyweight, female)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="36" t="inlineStr">
         <is>
           <t>Combat mixed</t>
         </is>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="36" t="n">
         <v>160</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G130" s="36" t="n">
         <v>54</v>
       </c>
-      <c r="H130" t="n">
+      <c r="H130" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I130" t="n">
+      <c r="I130" s="36" t="n">
         <v>21.1</v>
       </c>
-      <c r="J130" t="n">
+      <c r="J130" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="K130" t="n">
+      <c r="K130" s="36" t="n">
         <v>0.985</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M130" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N130" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="O130" t="n">
+      <c r="O130" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P130" t="n">
+      <c r="P130" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="Q130" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R130" t="n">
+      <c r="R130" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="S130" t="n">
+      <c r="S130" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T130" t="n">
+      <c r="T130" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U130" t="n">
+      <c r="U130" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V130" t="n">
+      <c r="V130" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W130" t="inlineStr">
+      <c r="W130" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="X130" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Y130" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
+      <c r="Z130" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA130" t="inlineStr">
+      <c r="AA130" s="36" t="inlineStr">
         <is>
           <t>16+</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
+      <c r="AB130" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC130" t="n">
+      <c r="AC130" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD130" t="inlineStr">
+      <c r="AD130" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE130" t="inlineStr">
+      <c r="AE130" s="36" t="inlineStr">
         <is>
           <t>UFC athlete data; Scoggin JF et al. (2010) Phys Sportsmed.</t>
         </is>
       </c>
-      <c r="AF130" t="inlineStr">
+      <c r="AF130" s="36" t="inlineStr">
         <is>
           <t>UFC women's divisions (SW–FW): 52–61 kg, ~160–165 cm. Demands identical to male (striking + grappling).</t>
         </is>
       </c>
-      <c r="AG130" t="inlineStr">
+      <c r="AG130" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="36" t="inlineStr">
         <is>
           <t>SP16F</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="36" t="inlineStr">
         <is>
           <t>Brazilian jiu-jitsu</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="36" t="inlineStr">
         <is>
           <t>Combat grappling</t>
         </is>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="36" t="n">
         <v>162</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G131" t="n">
+      <c r="G131" s="36" t="n">
         <v>58</v>
       </c>
-      <c r="H131" t="n">
+      <c r="H131" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I131" t="n">
+      <c r="I131" s="36" t="n">
         <v>22.1</v>
       </c>
-      <c r="J131" t="n">
+      <c r="J131" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="M131" t="n">
+      <c r="M131" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="N131" t="n">
+      <c r="N131" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O131" t="n">
+      <c r="O131" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P131" t="n">
+      <c r="P131" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q131" t="n">
+      <c r="Q131" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="R131" t="n">
+      <c r="R131" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="S131" t="n">
+      <c r="S131" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="T131" t="n">
+      <c r="T131" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="U131" t="n">
+      <c r="U131" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V131" t="n">
+      <c r="V131" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W131" t="inlineStr">
+      <c r="W131" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="X131" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Y131" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
+      <c r="Z131" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA131" t="inlineStr">
+      <c r="AA131" s="36" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
+      <c r="AB131" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC131" t="n">
+      <c r="AC131" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD131" t="inlineStr">
+      <c r="AD131" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE131" t="inlineStr">
+      <c r="AE131" s="36" t="inlineStr">
         <is>
           <t>Andreato LV et al. (2016) Arch Budo; IBJJF competition data.</t>
         </is>
       </c>
-      <c r="AF131" t="inlineStr">
+      <c r="AF131" s="36" t="inlineStr">
         <is>
           <t>IBJJF female elite: technique-dominant, sex performance gap narrower than strength sports. Andreato et al. (2016).</t>
         </is>
       </c>
-      <c r="AG131" t="inlineStr">
+      <c r="AG131" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="36" t="inlineStr">
         <is>
           <t>SP17F</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="36" t="inlineStr">
         <is>
           <t>Wrestling (freestyle)</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="36" t="inlineStr">
         <is>
           <t>Combat grappling</t>
         </is>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="36" t="n">
         <v>157</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G132" s="36" t="n">
         <v>63</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H132" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="I132" t="n">
+      <c r="I132" s="36" t="n">
         <v>25.6</v>
       </c>
-      <c r="J132" t="n">
+      <c r="J132" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M132" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N132" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="O132" t="n">
+      <c r="O132" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P132" t="n">
+      <c r="P132" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q132" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R132" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S132" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="T132" t="n">
+      <c r="T132" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U132" t="n">
+      <c r="U132" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V132" t="n">
+      <c r="V132" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W132" t="inlineStr">
+      <c r="W132" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
+      <c r="X132" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Y132" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
+      <c r="Z132" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA132" t="inlineStr">
+      <c r="AA132" s="36" t="inlineStr">
         <is>
           <t>8–16</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
+      <c r="AB132" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC132" t="n">
+      <c r="AC132" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD132" t="inlineStr">
+      <c r="AD132" s="36" t="inlineStr">
         <is>
           <t>Some</t>
         </is>
       </c>
-      <c r="AE132" t="inlineStr">
+      <c r="AE132" s="36" t="inlineStr">
         <is>
           <t>UWW official data; derived from SP17 via sex differentials (Holway &amp; Sprague 2011).</t>
         </is>
       </c>
-      <c r="AF132" t="inlineStr">
+      <c r="AF132" s="36" t="inlineStr">
         <is>
           <t>Female freestyle wrestling elite: lighter and shorter. World Wrestling Federation data; same technical demands as male division.</t>
         </is>
       </c>
-      <c r="AG132" t="inlineStr">
+      <c r="AG132" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="36" t="inlineStr">
         <is>
           <t>SP18F</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="36" t="inlineStr">
         <is>
           <t>Taekwondo</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="36" t="inlineStr">
         <is>
           <t>Combat striking</t>
         </is>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="36" t="n">
         <v>166</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G133" t="n">
+      <c r="G133" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="H133" t="n">
+      <c r="H133" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I133" t="n">
+      <c r="I133" s="36" t="n">
         <v>20.3</v>
       </c>
-      <c r="J133" t="n">
+      <c r="J133" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="M133" t="n">
+      <c r="M133" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N133" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="O133" t="n">
+      <c r="O133" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P133" t="n">
+      <c r="P133" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q133" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R133" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S133" t="n">
+      <c r="S133" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="T133" t="n">
+      <c r="T133" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U133" t="n">
+      <c r="U133" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="V133" t="n">
+      <c r="V133" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W133" t="inlineStr">
+      <c r="W133" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr">
+      <c r="X133" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Y133" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
+      <c r="Z133" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA133" t="inlineStr">
+      <c r="AA133" s="36" t="inlineStr">
         <is>
           <t>6–14</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
+      <c r="AB133" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC133" t="n">
+      <c r="AC133" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD133" t="inlineStr">
+      <c r="AD133" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE133" t="inlineStr">
+      <c r="AE133" s="36" t="inlineStr">
         <is>
           <t>World Taekwondo Federation data; derived from SP18 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF133" t="inlineStr">
+      <c r="AF133" s="36" t="inlineStr">
         <is>
           <t>WT female athletes: lighter, shorter than male. Olympic 57 kg class typical. Demands identical; kick-dominated scoring same.</t>
         </is>
       </c>
-      <c r="AG133" t="inlineStr">
+      <c r="AG133" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="36" t="inlineStr">
         <is>
           <t>SP19F</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="36" t="inlineStr">
         <is>
           <t>Kickboxing</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="36" t="inlineStr">
         <is>
           <t>Pro light/super-light (female)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="36" t="inlineStr">
         <is>
           <t>Combat striking</t>
         </is>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="36" t="n">
         <v>163</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G134" t="n">
+      <c r="G134" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="H134" t="n">
+      <c r="H134" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I134" t="n">
+      <c r="I134" s="36" t="n">
         <v>22.6</v>
       </c>
-      <c r="J134" t="n">
+      <c r="J134" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="M134" t="n">
+      <c r="M134" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N134" t="n">
+      <c r="N134" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="O134" t="n">
+      <c r="O134" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P134" t="n">
+      <c r="P134" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q134" t="n">
+      <c r="Q134" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="R134" t="n">
+      <c r="R134" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="S134" t="n">
+      <c r="S134" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="T134" t="n">
+      <c r="T134" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U134" t="n">
+      <c r="U134" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="V134" t="n">
+      <c r="V134" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W134" t="inlineStr">
+      <c r="W134" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="X134" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Y134" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
+      <c r="Z134" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA134" t="inlineStr">
+      <c r="AA134" s="36" t="inlineStr">
         <is>
           <t>12–18</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
+      <c r="AB134" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC134" t="n">
+      <c r="AC134" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD134" t="inlineStr">
+      <c r="AD134" s="36" t="inlineStr">
         <is>
           <t>Growing</t>
         </is>
       </c>
-      <c r="AE134" t="inlineStr">
+      <c r="AE134" s="36" t="inlineStr">
         <is>
           <t>WAKO / WKN data; derived from SP19 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF134" t="inlineStr">
+      <c r="AF134" s="36" t="inlineStr">
         <is>
           <t>Female kickboxing pro: strawweight–super-lightweight common. Demands identical to male.</t>
         </is>
       </c>
-      <c r="AG134" t="inlineStr">
+      <c r="AG134" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="36" t="inlineStr">
         <is>
           <t>SP21F</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="36" t="inlineStr">
         <is>
           <t>Squash</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" s="36" t="inlineStr">
         <is>
           <t>Individual racquet</t>
         </is>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="36" t="n">
         <v>166</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G135" s="36" t="n">
         <v>63</v>
       </c>
-      <c r="H135" t="n">
+      <c r="H135" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I135" t="n">
+      <c r="I135" s="36" t="n">
         <v>22.9</v>
       </c>
-      <c r="J135" t="n">
+      <c r="J135" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="M135" t="n">
+      <c r="M135" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="N135" t="n">
+      <c r="N135" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O135" t="n">
+      <c r="O135" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P135" t="n">
+      <c r="P135" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q135" t="n">
+      <c r="Q135" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R135" t="n">
+      <c r="R135" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="S135" t="n">
+      <c r="S135" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="T135" t="n">
+      <c r="T135" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U135" t="n">
+      <c r="U135" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V135" t="n">
+      <c r="V135" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W135" t="inlineStr">
+      <c r="W135" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
+      <c r="X135" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Y135" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
+      <c r="Z135" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA135" t="inlineStr">
+      <c r="AA135" s="36" t="inlineStr">
         <is>
           <t>10–18</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
+      <c r="AB135" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC135" t="n">
+      <c r="AC135" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD135" t="inlineStr">
+      <c r="AD135" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE135" t="inlineStr">
+      <c r="AE135" s="36" t="inlineStr">
         <is>
           <t>PSA World Tour data; derived from SP21 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF135" t="inlineStr">
+      <c r="AF135" s="36" t="inlineStr">
         <is>
           <t>PSA women's tour: slightly shorter/lighter than men, same technical demands.</t>
         </is>
       </c>
-      <c r="AG135" t="inlineStr">
+      <c r="AG135" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="36" t="inlineStr">
         <is>
           <t>SP22F</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="36" t="inlineStr">
         <is>
           <t>Table tennis</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" s="36" t="inlineStr">
         <is>
           <t>Individual racquet</t>
         </is>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="36" t="n">
         <v>163</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G136" t="n">
+      <c r="G136" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="H136" t="n">
+      <c r="H136" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I136" t="n">
+      <c r="I136" s="36" t="n">
         <v>22.6</v>
       </c>
-      <c r="J136" t="n">
+      <c r="J136" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="M136" t="n">
+      <c r="M136" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N136" t="n">
+      <c r="N136" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O136" t="n">
+      <c r="O136" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P136" t="n">
+      <c r="P136" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q136" t="n">
+      <c r="Q136" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R136" t="n">
+      <c r="R136" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S136" t="n">
+      <c r="S136" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T136" t="n">
+      <c r="T136" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="U136" t="n">
+      <c r="U136" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="V136" t="n">
+      <c r="V136" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W136" t="inlineStr">
+      <c r="W136" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
+      <c r="X136" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="Y136" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
+      <c r="Z136" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA136" t="inlineStr">
+      <c r="AA136" s="36" t="inlineStr">
         <is>
           <t>5–10</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
+      <c r="AB136" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC136" t="n">
+      <c r="AC136" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD136" t="inlineStr">
+      <c r="AD136" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE136" t="inlineStr">
+      <c r="AE136" s="36" t="inlineStr">
         <is>
           <t>ITTF data; derived from SP22 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF136" t="inlineStr">
+      <c r="AF136" s="36" t="inlineStr">
         <is>
           <t>ITTF women's tour: very similar demand profile. Korean/Chinese athletes typically shorter than simple scaling predicts.</t>
         </is>
       </c>
-      <c r="AG136" t="inlineStr">
+      <c r="AG136" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="36" t="inlineStr">
         <is>
           <t>SP23F</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="36" t="inlineStr">
         <is>
           <t>Powerlifting</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="36" t="inlineStr">
         <is>
           <t>Middleweight (~69–76 kg, female)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" s="36" t="inlineStr">
         <is>
           <t>Strength individual</t>
         </is>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="36" t="n">
         <v>162</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G137" t="n">
+      <c r="G137" s="36" t="n">
         <v>70</v>
       </c>
-      <c r="H137" t="n">
+      <c r="H137" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I137" t="n">
+      <c r="I137" s="36" t="n">
         <v>26.7</v>
       </c>
-      <c r="J137" t="n">
+      <c r="J137" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="M137" t="n">
+      <c r="M137" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="N137" t="n">
+      <c r="N137" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O137" t="n">
+      <c r="O137" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P137" t="n">
+      <c r="P137" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q137" t="n">
+      <c r="Q137" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="R137" t="n">
+      <c r="R137" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S137" t="n">
+      <c r="S137" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T137" t="n">
+      <c r="T137" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="U137" t="n">
+      <c r="U137" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V137" t="n">
+      <c r="V137" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W137" t="inlineStr">
+      <c r="W137" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X137" t="inlineStr">
+      <c r="X137" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="Y137" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
+      <c r="Z137" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA137" t="inlineStr">
+      <c r="AA137" s="36" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
+      <c r="AB137" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC137" t="n">
+      <c r="AC137" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD137" t="inlineStr">
+      <c r="AD137" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE137" t="inlineStr">
+      <c r="AE137" s="36" t="inlineStr">
         <is>
           <t>IPF official records; Sooneste H et al. (2021) Sports (Basel).</t>
         </is>
       </c>
-      <c r="AF137" t="inlineStr">
+      <c r="AF137" s="36" t="inlineStr">
         <is>
           <t>IPF women's powerlifting: higher BF than male at equivalent weight class. Total demands profile identical.</t>
         </is>
       </c>
-      <c r="AG137" t="inlineStr">
+      <c r="AG137" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="36" t="inlineStr">
         <is>
           <t>SP24F</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="36" t="inlineStr">
         <is>
           <t>Olympic weightlifting</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="36" t="inlineStr">
         <is>
           <t>Middleweight (~64–71 kg, female)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" s="36" t="inlineStr">
         <is>
           <t>Strength individual</t>
         </is>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="36" t="n">
         <v>162</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G138" t="n">
+      <c r="G138" s="36" t="n">
         <v>67</v>
       </c>
-      <c r="H138" t="n">
+      <c r="H138" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I138" t="n">
+      <c r="I138" s="36" t="n">
         <v>25.5</v>
       </c>
-      <c r="J138" t="n">
+      <c r="J138" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="M138" t="n">
+      <c r="M138" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="N138" t="n">
+      <c r="N138" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="O138" t="n">
+      <c r="O138" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P138" t="n">
+      <c r="P138" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="Q138" t="n">
+      <c r="Q138" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R138" t="n">
+      <c r="R138" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S138" t="n">
+      <c r="S138" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="T138" t="n">
+      <c r="T138" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U138" t="n">
+      <c r="U138" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V138" t="n">
+      <c r="V138" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W138" t="inlineStr">
+      <c r="W138" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr">
+      <c r="X138" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Y138" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
+      <c r="Z138" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA138" t="inlineStr">
+      <c r="AA138" s="36" t="inlineStr">
         <is>
           <t>10–16</t>
         </is>
       </c>
-      <c r="AB138" t="inlineStr">
+      <c r="AB138" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC138" t="n">
+      <c r="AC138" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD138" t="inlineStr">
+      <c r="AD138" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE138" t="inlineStr">
+      <c r="AE138" s="36" t="inlineStr">
         <is>
           <t>IWF official data; Marchetti PH et al. (2016) J Hum Kinet.</t>
         </is>
       </c>
-      <c r="AF138" t="inlineStr">
+      <c r="AF138" s="36" t="inlineStr">
         <is>
           <t>IWF women's 64 kg class: 160–165 cm. Exceptional power-to-weight, high lean mass.</t>
         </is>
       </c>
-      <c r="AG138" t="inlineStr">
+      <c r="AG138" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="36" t="inlineStr">
         <is>
           <t>SP25F</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="36" t="inlineStr">
         <is>
           <t>Strongman</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="36" t="inlineStr">
         <is>
           <t>Elite open class (female)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="36" t="inlineStr">
         <is>
           <t>Strength individual</t>
         </is>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="36" t="n">
         <v>172</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139" s="36" t="n">
         <v>7.1</v>
       </c>
-      <c r="G139" t="n">
+      <c r="G139" s="36" t="n">
         <v>128</v>
       </c>
-      <c r="H139" t="n">
+      <c r="H139" s="36" t="n">
         <v>19.3</v>
       </c>
-      <c r="I139" t="n">
+      <c r="I139" s="36" t="n">
         <v>43.3</v>
       </c>
-      <c r="J139" t="n">
+      <c r="J139" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="M139" t="n">
+      <c r="M139" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N139" t="n">
+      <c r="N139" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O139" t="n">
+      <c r="O139" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P139" t="n">
+      <c r="P139" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q139" t="n">
+      <c r="Q139" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="R139" t="n">
+      <c r="R139" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="S139" t="n">
+      <c r="S139" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="T139" t="n">
+      <c r="T139" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="U139" t="n">
+      <c r="U139" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V139" t="n">
+      <c r="V139" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W139" t="inlineStr">
+      <c r="W139" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
+      <c r="X139" s="36" t="inlineStr">
         <is>
           <t>Outdoor / indoor</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Y139" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
+      <c r="Z139" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA139" t="inlineStr">
+      <c r="AA139" s="36" t="inlineStr">
         <is>
           <t>20+</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
+      <c r="AB139" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC139" t="n">
+      <c r="AC139" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD139" t="inlineStr">
+      <c r="AD139" s="36" t="inlineStr">
         <is>
           <t>Some</t>
         </is>
       </c>
-      <c r="AE139" t="inlineStr">
+      <c r="AE139" s="36" t="inlineStr">
         <is>
           <t>WSW competition data; derived from SP25 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF139" t="inlineStr">
+      <c r="AF139" s="36" t="inlineStr">
         <is>
           <t>Strongwoman competitors are significantly lighter than male counterparts. World's Strongest Woman field: ~100–135 kg, 170–175 cm. BF higher than male Strongman. Same demands — maximal strength dominant.</t>
         </is>
       </c>
-      <c r="AG139" t="inlineStr">
+      <c r="AG139" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="36" t="inlineStr">
         <is>
           <t>SP27F</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="36" t="inlineStr">
         <is>
           <t>Biathlon</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C140" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" s="36" t="inlineStr">
         <is>
           <t>Endurance individual / pursuit</t>
         </is>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="36" t="n">
         <v>167</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G140" s="36" t="n">
         <v>61</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H140" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I140" t="n">
+      <c r="I140" s="36" t="n">
         <v>21.9</v>
       </c>
-      <c r="J140" t="n">
+      <c r="J140" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M140" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N140" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O140" t="n">
+      <c r="O140" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P140" t="n">
+      <c r="P140" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="Q140" t="n">
+      <c r="Q140" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="R140" t="n">
+      <c r="R140" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="S140" t="n">
+      <c r="S140" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T140" t="n">
+      <c r="T140" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U140" t="n">
+      <c r="U140" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V140" t="n">
+      <c r="V140" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W140" t="inlineStr">
+      <c r="W140" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X140" t="inlineStr">
+      <c r="X140" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Y140" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
+      <c r="Z140" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA140" t="inlineStr">
+      <c r="AA140" s="36" t="inlineStr">
         <is>
           <t>8–14</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
+      <c r="AB140" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC140" t="n">
+      <c r="AC140" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="AD140" t="inlineStr">
+      <c r="AD140" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE140" t="inlineStr">
+      <c r="AE140" s="36" t="inlineStr">
         <is>
           <t>IBU official data; derived from SP27 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF140" t="inlineStr">
+      <c r="AF140" s="36" t="inlineStr">
         <is>
           <t>IBU biathlon women's circuit: lighter than male but same aerobic + rifle demand structure.</t>
         </is>
       </c>
-      <c r="AG140" t="inlineStr">
+      <c r="AG140" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="36" t="inlineStr">
         <is>
           <t>SP28F</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="36" t="inlineStr">
         <is>
           <t>Alpine skiing</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="36" t="inlineStr">
         <is>
           <t>Technical (slalom / GS, female)</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" s="36" t="inlineStr">
         <is>
           <t>Power-speed individual</t>
         </is>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="36" t="n">
         <v>164</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G141" s="36" t="n">
         <v>67</v>
       </c>
-      <c r="H141" t="n">
+      <c r="H141" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I141" t="n">
+      <c r="I141" s="36" t="n">
         <v>24.9</v>
       </c>
-      <c r="J141" t="n">
+      <c r="J141" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="M141" t="n">
+      <c r="M141" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N141" t="n">
+      <c r="N141" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O141" t="n">
+      <c r="O141" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="P141" t="n">
+      <c r="P141" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q141" t="n">
+      <c r="Q141" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R141" t="n">
+      <c r="R141" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="S141" t="n">
+      <c r="S141" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T141" t="n">
+      <c r="T141" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U141" t="n">
+      <c r="U141" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V141" t="n">
+      <c r="V141" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W141" t="inlineStr">
+      <c r="W141" s="36" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="X141" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Y141" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
+      <c r="Z141" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA141" t="inlineStr">
+      <c r="AA141" s="36" t="inlineStr">
         <is>
           <t>5–10</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
+      <c r="AB141" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC141" t="n">
+      <c r="AC141" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="AD141" t="inlineStr">
+      <c r="AD141" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE141" t="inlineStr">
+      <c r="AE141" s="36" t="inlineStr">
         <is>
           <t>FIS data; derived from SP28 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF141" t="inlineStr">
+      <c r="AF141" s="36" t="inlineStr">
         <is>
           <t>FIS women's alpine tech events: similar demand to male, physically lighter.</t>
         </is>
       </c>
-      <c r="AG141" t="inlineStr">
+      <c r="AG141" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="36" t="inlineStr">
         <is>
           <t>SP28bF</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="36" t="inlineStr">
         <is>
           <t>Alpine skiing</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="36" t="inlineStr">
         <is>
           <t>Speed (super-G / downhill, female)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" s="36" t="inlineStr">
         <is>
           <t>Power-speed individual</t>
         </is>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="36" t="n">
         <v>169</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" s="36" t="n">
         <v>74</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H142" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I142" t="n">
+      <c r="I142" s="36" t="n">
         <v>25.9</v>
       </c>
-      <c r="J142" t="n">
+      <c r="J142" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="M142" t="n">
+      <c r="M142" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N142" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O142" t="n">
+      <c r="O142" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="P142" t="n">
+      <c r="P142" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q142" t="n">
+      <c r="Q142" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R142" t="n">
+      <c r="R142" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S142" t="n">
+      <c r="S142" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T142" t="n">
+      <c r="T142" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U142" t="n">
+      <c r="U142" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V142" t="n">
+      <c r="V142" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W142" t="inlineStr">
+      <c r="W142" s="36" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
+      <c r="X142" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="Y142" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
+      <c r="Z142" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA142" t="inlineStr">
+      <c r="AA142" s="36" t="inlineStr">
         <is>
           <t>5–10</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
+      <c r="AB142" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC142" t="n">
+      <c r="AC142" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="AD142" t="inlineStr">
+      <c r="AD142" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE142" t="inlineStr">
+      <c r="AE142" s="36" t="inlineStr">
         <is>
           <t>FIS data; derived from SP28b via sex differentials.</t>
         </is>
       </c>
-      <c r="AF142" t="inlineStr">
+      <c r="AF142" s="36" t="inlineStr">
         <is>
           <t>FIS women's speed events: slightly less massive than men's speed skiers but same demands.</t>
         </is>
       </c>
-      <c r="AG142" t="inlineStr">
+      <c r="AG142" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="36" t="inlineStr">
         <is>
           <t>SP31F</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="36" t="inlineStr">
         <is>
           <t>Kayaking</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="36" t="inlineStr">
         <is>
           <t>Sprint (female)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="36" t="inlineStr">
         <is>
           <t>Endurance individual / pair</t>
         </is>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="36" t="n">
         <v>166</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G143" t="n">
+      <c r="G143" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="H143" t="n">
+      <c r="H143" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I143" t="n">
+      <c r="I143" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="J143" t="n">
+      <c r="J143" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="K143" t="n">
+      <c r="K143" s="36" t="n">
         <v>1.05</v>
       </c>
-      <c r="M143" t="n">
+      <c r="M143" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N143" t="n">
+      <c r="N143" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O143" t="n">
+      <c r="O143" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P143" t="n">
+      <c r="P143" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q143" t="n">
+      <c r="Q143" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R143" t="n">
+      <c r="R143" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="S143" t="n">
+      <c r="S143" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T143" t="n">
+      <c r="T143" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="U143" t="n">
+      <c r="U143" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="V143" t="n">
+      <c r="V143" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W143" t="inlineStr">
+      <c r="W143" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
+      <c r="X143" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
+      <c r="Y143" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
+      <c r="Z143" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA143" t="inlineStr">
+      <c r="AA143" s="36" t="inlineStr">
         <is>
           <t>8–14</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
+      <c r="AB143" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC143" t="n">
+      <c r="AC143" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD143" t="inlineStr">
+      <c r="AD143" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE143" t="inlineStr">
+      <c r="AE143" s="36" t="inlineStr">
         <is>
           <t>ICF data; derived from SP31 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF143" t="inlineStr">
+      <c r="AF143" s="36" t="inlineStr">
         <is>
           <t>ICF women's kayak sprint. Demands identical.</t>
         </is>
       </c>
-      <c r="AG143" t="inlineStr">
+      <c r="AG143" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="36" t="inlineStr">
         <is>
           <t>SP45F</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="36" t="inlineStr">
         <is>
           <t>Discus throw</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="36" t="inlineStr">
         <is>
           <t>Power-throw individual</t>
         </is>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="36" t="n">
         <v>178</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G144" t="n">
+      <c r="G144" s="36" t="n">
         <v>92</v>
       </c>
-      <c r="H144" t="n">
+      <c r="H144" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="I144" t="n">
+      <c r="I144" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="J144" t="n">
+      <c r="J144" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="K144" t="n">
+      <c r="K144" s="36" t="n">
         <v>1.04</v>
       </c>
-      <c r="M144" t="n">
+      <c r="M144" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="N144" t="n">
+      <c r="N144" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O144" t="n">
+      <c r="O144" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P144" t="n">
+      <c r="P144" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="Q144" t="n">
+      <c r="Q144" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R144" t="n">
+      <c r="R144" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="S144" t="n">
+      <c r="S144" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T144" t="n">
+      <c r="T144" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U144" t="n">
+      <c r="U144" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V144" t="n">
+      <c r="V144" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W144" t="inlineStr">
+      <c r="W144" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
+      <c r="X144" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="Y144" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
+      <c r="Z144" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA144" t="inlineStr">
+      <c r="AA144" s="36" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
+      <c r="AB144" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC144" t="n">
+      <c r="AC144" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="AD144" t="inlineStr">
+      <c r="AD144" s="36" t="inlineStr">
         <is>
           <t>Some</t>
         </is>
       </c>
-      <c r="AE144" t="inlineStr">
+      <c r="AE144" s="36" t="inlineStr">
         <is>
           <t>World Athletics data; derived from SP45 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF144" t="inlineStr">
+      <c r="AF144" s="36" t="inlineStr">
         <is>
           <t>IAAF women's discus: shorter implement, lighter implement (1 kg vs 2 kg male). Physical profile lighter; power demands equal.</t>
         </is>
       </c>
-      <c r="AG144" t="inlineStr">
+      <c r="AG144" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="36" t="inlineStr">
         <is>
           <t>SP46F</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="36" t="inlineStr">
         <is>
           <t>Shot put</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="36" t="inlineStr">
         <is>
           <t>Power-throw individual</t>
         </is>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="36" t="n">
         <v>173</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G145" t="n">
+      <c r="G145" s="36" t="n">
         <v>102</v>
       </c>
-      <c r="H145" t="n">
+      <c r="H145" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="I145" t="n">
+      <c r="I145" s="36" t="n">
         <v>34.1</v>
       </c>
-      <c r="J145" t="n">
+      <c r="J145" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="M145" t="n">
+      <c r="M145" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="N145" t="n">
+      <c r="N145" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O145" t="n">
+      <c r="O145" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="P145" t="n">
+      <c r="P145" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="Q145" t="n">
+      <c r="Q145" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="R145" t="n">
+      <c r="R145" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S145" t="n">
+      <c r="S145" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T145" t="n">
+      <c r="T145" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U145" t="n">
+      <c r="U145" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V145" t="n">
+      <c r="V145" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W145" t="inlineStr">
+      <c r="W145" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
+      <c r="X145" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="Y145" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
+      <c r="Z145" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA145" t="inlineStr">
+      <c r="AA145" s="36" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
+      <c r="AB145" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC145" t="n">
+      <c r="AC145" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="AD145" t="inlineStr">
+      <c r="AD145" s="36" t="inlineStr">
         <is>
           <t>Some</t>
         </is>
       </c>
-      <c r="AE145" t="inlineStr">
+      <c r="AE145" s="36" t="inlineStr">
         <is>
           <t>World Athletics data; derived from SP46 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF145" t="inlineStr">
+      <c r="AF145" s="36" t="inlineStr">
         <is>
           <t>IAAF women's shot put: 4 kg implement vs 7.26 kg male. Physical profile lighter; strength demands equal.</t>
         </is>
       </c>
-      <c r="AG145" t="inlineStr">
+      <c r="AG145" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="36" t="inlineStr">
         <is>
           <t>SP49F</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="36" t="inlineStr">
         <is>
           <t>Triple jump</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="36" t="inlineStr">
         <is>
           <t>Senior elite (female)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" s="36" t="inlineStr">
         <is>
           <t>Power-jump individual</t>
         </is>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="36" t="n">
         <v>173</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G146" t="n">
+      <c r="G146" s="36" t="n">
         <v>67</v>
       </c>
-      <c r="H146" t="n">
+      <c r="H146" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I146" t="n">
+      <c r="I146" s="36" t="n">
         <v>22.4</v>
       </c>
-      <c r="J146" t="n">
+      <c r="J146" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="M146" t="n">
+      <c r="M146" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N146" t="n">
+      <c r="N146" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="O146" t="n">
+      <c r="O146" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="P146" t="n">
+      <c r="P146" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="Q146" t="n">
+      <c r="Q146" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="R146" t="n">
+      <c r="R146" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S146" t="n">
+      <c r="S146" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T146" t="n">
+      <c r="T146" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U146" t="n">
+      <c r="U146" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V146" t="n">
+      <c r="V146" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W146" t="inlineStr">
+      <c r="W146" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
+      <c r="X146" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="Y146" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
+      <c r="Z146" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA146" t="inlineStr">
+      <c r="AA146" s="36" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
+      <c r="AB146" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC146" t="n">
+      <c r="AC146" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="AD146" t="inlineStr">
+      <c r="AD146" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE146" t="inlineStr">
+      <c r="AE146" s="36" t="inlineStr">
         <is>
           <t>World Athletics data; derived from SP49 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF146" t="inlineStr">
+      <c r="AF146" s="36" t="inlineStr">
         <is>
           <t>IAAF women's triple jump: demands identical to male, physical profile lighter.</t>
         </is>
       </c>
-      <c r="AG146" t="inlineStr">
+      <c r="AG146" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="36" t="inlineStr">
         <is>
           <t>SP57F</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="36" t="inlineStr">
         <is>
           <t>Padel</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C147" s="36" t="inlineStr">
         <is>
           <t>Doubles (female)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" s="36" t="inlineStr">
         <is>
           <t>Individual racquet</t>
         </is>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="36" t="n">
         <v>161</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G147" t="n">
+      <c r="G147" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="H147" t="n">
+      <c r="H147" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I147" t="n">
+      <c r="I147" s="36" t="n">
         <v>23.9</v>
       </c>
-      <c r="J147" t="n">
+      <c r="J147" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="M147" t="n">
+      <c r="M147" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N147" t="n">
+      <c r="N147" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O147" t="n">
+      <c r="O147" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="P147" t="n">
+      <c r="P147" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="Q147" t="n">
+      <c r="Q147" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="R147" t="n">
+      <c r="R147" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S147" t="n">
+      <c r="S147" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T147" t="n">
+      <c r="T147" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U147" t="n">
+      <c r="U147" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V147" t="n">
+      <c r="V147" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="W147" t="inlineStr">
+      <c r="W147" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X147" t="inlineStr">
+      <c r="X147" s="36" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="Y147" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
+      <c r="Z147" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
+      <c r="AA147" s="36" t="inlineStr">
         <is>
           <t>8–60</t>
         </is>
       </c>
-      <c r="AB147" t="inlineStr">
+      <c r="AB147" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC147" t="n">
+      <c r="AC147" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD147" t="inlineStr">
+      <c r="AD147" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE147" t="inlineStr">
+      <c r="AE147" s="36" t="inlineStr">
         <is>
           <t>WPT Tour data; derived from SP57 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF147" t="inlineStr">
+      <c r="AF147" s="36" t="inlineStr">
         <is>
           <t>WPT women's padel: same court / racket / demands. Physical profile slightly shorter.</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
+      <c r="AG147" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="36" t="inlineStr">
         <is>
           <t>SP58BF</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="36" t="inlineStr">
         <is>
           <t>Volleyball (Beach)</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C148" s="36" t="inlineStr">
         <is>
           <t>Beach (2-a-side, female)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" s="36" t="inlineStr">
         <is>
           <t>Team court</t>
         </is>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="36" t="n">
         <v>177</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G148" t="n">
+      <c r="G148" s="36" t="n">
         <v>72</v>
       </c>
-      <c r="H148" t="n">
+      <c r="H148" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I148" t="n">
+      <c r="I148" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="J148" t="n">
+      <c r="J148" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="M148" t="n">
+      <c r="M148" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N148" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O148" t="n">
+      <c r="O148" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P148" t="n">
+      <c r="P148" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q148" t="n">
+      <c r="Q148" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="R148" t="n">
+      <c r="R148" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="S148" t="n">
+      <c r="S148" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T148" t="n">
+      <c r="T148" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U148" t="n">
+      <c r="U148" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V148" t="n">
+      <c r="V148" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="W148" t="inlineStr">
+      <c r="W148" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
+      <c r="X148" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="Y148" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
+      <c r="Z148" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA148" t="inlineStr">
+      <c r="AA148" s="36" t="inlineStr">
         <is>
           <t>10–18</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
+      <c r="AB148" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC148" t="n">
+      <c r="AC148" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="AD148" t="inlineStr">
+      <c r="AD148" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE148" t="inlineStr">
+      <c r="AE148" s="36" t="inlineStr">
         <is>
           <t>FIVB data; derived from SP58B via sex differentials.</t>
         </is>
       </c>
-      <c r="AF148" t="inlineStr">
+      <c r="AF148" s="36" t="inlineStr">
         <is>
           <t>FIVB women's beach volleyball: slightly shorter/lighter than male, same court demands.</t>
         </is>
       </c>
-      <c r="AG148" t="inlineStr">
+      <c r="AG148" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="36" t="inlineStr">
         <is>
           <t>SP59F</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="36" t="inlineStr">
         <is>
           <t>Calisthenics</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="36" t="inlineStr">
         <is>
           <t>Freestyle / Competition (female)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" s="36" t="inlineStr">
         <is>
           <t>Strength individual</t>
         </is>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="36" t="n">
         <v>160</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G149" t="n">
+      <c r="G149" s="36" t="n">
         <v>57</v>
       </c>
-      <c r="H149" t="n">
+      <c r="H149" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I149" t="n">
+      <c r="I149" s="36" t="n">
         <v>22.3</v>
       </c>
-      <c r="J149" t="n">
+      <c r="J149" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="M149" t="n">
+      <c r="M149" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="N149" t="n">
+      <c r="N149" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="O149" t="n">
+      <c r="O149" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P149" t="n">
+      <c r="P149" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q149" t="n">
+      <c r="Q149" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="R149" t="n">
+      <c r="R149" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S149" t="n">
+      <c r="S149" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="T149" t="n">
+      <c r="T149" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U149" t="n">
+      <c r="U149" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="V149" t="n">
+      <c r="V149" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W149" t="inlineStr">
+      <c r="W149" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
+      <c r="X149" s="36" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Y149" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
+      <c r="Z149" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
+      <c r="AA149" s="36" t="inlineStr">
         <is>
           <t>10–20</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
+      <c r="AB149" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC149" t="n">
+      <c r="AC149" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD149" t="inlineStr">
+      <c r="AD149" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
+      <c r="AE149" s="36" t="inlineStr">
         <is>
           <t>Derived from SP59 via sex differentials (Holway &amp; Sprague 2011).</t>
         </is>
       </c>
-      <c r="AF149" t="inlineStr">
+      <c r="AF149" s="36" t="inlineStr">
         <is>
           <t>Female calisthenics athletes: same relative demand profile, lighter frame.</t>
         </is>
       </c>
-      <c r="AG149" t="inlineStr">
+      <c r="AG149" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="36" t="inlineStr">
         <is>
           <t>SP60F</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="36" t="inlineStr">
         <is>
           <t>Mountain Biking</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="36" t="inlineStr">
         <is>
           <t>XC / Trail (female)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="36" t="inlineStr">
         <is>
           <t>Endurance individual</t>
         </is>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="36" t="n">
         <v>161</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G150" t="n">
+      <c r="G150" s="36" t="n">
         <v>57</v>
       </c>
-      <c r="H150" t="n">
+      <c r="H150" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I150" t="n">
+      <c r="I150" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="J150" t="n">
+      <c r="J150" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="M150" t="n">
+      <c r="M150" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N150" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="O150" t="n">
+      <c r="O150" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="P150" t="n">
+      <c r="P150" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="Q150" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="R150" t="n">
+      <c r="R150" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="S150" t="n">
+      <c r="S150" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="T150" t="n">
+      <c r="T150" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="U150" t="n">
+      <c r="U150" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V150" t="n">
+      <c r="V150" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W150" t="inlineStr">
+      <c r="W150" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X150" t="inlineStr">
+      <c r="X150" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="Y150" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
+      <c r="Z150" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
+      <c r="AA150" s="36" t="inlineStr">
         <is>
           <t>8–18</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
+      <c r="AB150" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC150" t="n">
+      <c r="AC150" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AD150" t="inlineStr">
+      <c r="AD150" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE150" t="inlineStr">
+      <c r="AE150" s="36" t="inlineStr">
         <is>
           <t>UCI data; derived from SP60 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF150" t="inlineStr">
+      <c r="AF150" s="36" t="inlineStr">
         <is>
           <t>UCI women's mountain bike: same aerobic + technical demands, lighter frame.</t>
         </is>
       </c>
-      <c r="AG150" t="inlineStr">
+      <c r="AG150" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="36" t="inlineStr">
         <is>
           <t>SP61F</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="36" t="inlineStr">
         <is>
           <t>Parkour / Freerunning</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="36" t="inlineStr">
         <is>
           <t>Freestyle (female)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" s="36" t="inlineStr">
         <is>
           <t>Power-skill individual</t>
         </is>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="36" t="n">
         <v>159</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G151" t="n">
+      <c r="G151" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="H151" t="n">
+      <c r="H151" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I151" t="n">
+      <c r="I151" s="36" t="n">
         <v>22.2</v>
       </c>
-      <c r="J151" t="n">
+      <c r="J151" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="M151" t="n">
+      <c r="M151" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N151" t="n">
+      <c r="N151" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O151" t="n">
+      <c r="O151" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P151" t="n">
+      <c r="P151" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="Q151" t="n">
+      <c r="Q151" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="R151" t="n">
+      <c r="R151" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="S151" t="n">
+      <c r="S151" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="T151" t="n">
+      <c r="T151" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U151" t="n">
+      <c r="U151" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V151" t="n">
+      <c r="V151" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="W151" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
+      <c r="X151" s="36" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
+      <c r="Y151" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
+      <c r="Z151" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA151" t="inlineStr">
+      <c r="AA151" s="36" t="inlineStr">
         <is>
           <t>8–18</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
+      <c r="AB151" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC151" t="n">
+      <c r="AC151" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD151" t="inlineStr">
+      <c r="AD151" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE151" t="inlineStr">
+      <c r="AE151" s="36" t="inlineStr">
         <is>
           <t>Derived from SP61 via sex differentials (Holway &amp; Sprague 2011).</t>
         </is>
       </c>
-      <c r="AF151" t="inlineStr">
+      <c r="AF151" s="36" t="inlineStr">
         <is>
           <t>Parkour has no formal elite standard; female practitioners follow the same skill demand curve.</t>
         </is>
       </c>
-      <c r="AG151" t="inlineStr">
+      <c r="AG151" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="36" t="inlineStr">
         <is>
           <t>SP62F</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="36" t="inlineStr">
         <is>
           <t>Hyrox</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C152" s="36" t="inlineStr">
         <is>
           <t>Individual (female)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D152" s="36" t="inlineStr">
         <is>
           <t>Endurance multi</t>
         </is>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="36" t="n">
         <v>168</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G152" t="n">
+      <c r="G152" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="H152" t="n">
+      <c r="H152" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I152" t="n">
+      <c r="I152" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="J152" t="n">
+      <c r="J152" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="M152" t="n">
+      <c r="M152" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="N152" t="n">
+      <c r="N152" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O152" t="n">
+      <c r="O152" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P152" t="n">
+      <c r="P152" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="Q152" t="n">
+      <c r="Q152" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R152" t="n">
+      <c r="R152" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="S152" t="n">
+      <c r="S152" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="T152" t="n">
+      <c r="T152" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="U152" t="n">
+      <c r="U152" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="V152" t="n">
+      <c r="V152" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W152" t="inlineStr">
+      <c r="W152" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X152" t="inlineStr">
+      <c r="X152" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
+      <c r="Y152" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
+      <c r="Z152" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA152" t="inlineStr">
+      <c r="AA152" s="36" t="inlineStr">
         <is>
           <t>16–35</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
+      <c r="AB152" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC152" t="n">
+      <c r="AC152" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD152" t="inlineStr">
+      <c r="AD152" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE152" t="inlineStr">
+      <c r="AE152" s="36" t="inlineStr">
         <is>
           <t>HYROX official race data (2023–2024).</t>
         </is>
       </c>
-      <c r="AF152" t="inlineStr">
+      <c r="AF152" s="36" t="inlineStr">
         <is>
           <t>HYROX female field: aerobic endurance build, slightly lighter than male field. Demands profile identical.</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
+      <c r="AG152" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="36" t="inlineStr">
         <is>
           <t>SP63F</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="36" t="inlineStr">
         <is>
           <t>CrossFit</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C153" s="36" t="inlineStr">
         <is>
           <t>WOD / Competition (female)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D153" s="36" t="inlineStr">
         <is>
           <t>Endurance multi</t>
         </is>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="36" t="n">
         <v>165</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G153" t="n">
+      <c r="G153" s="36" t="n">
         <v>65</v>
       </c>
-      <c r="H153" t="n">
+      <c r="H153" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="I153" t="n">
+      <c r="I153" s="36" t="n">
         <v>23.9</v>
       </c>
-      <c r="J153" t="n">
+      <c r="J153" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="M153" t="n">
+      <c r="M153" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N153" t="n">
+      <c r="N153" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O153" t="n">
+      <c r="O153" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="P153" t="n">
+      <c r="P153" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q153" t="n">
+      <c r="Q153" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R153" t="n">
+      <c r="R153" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S153" t="n">
+      <c r="S153" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T153" t="n">
+      <c r="T153" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="U153" t="n">
+      <c r="U153" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V153" t="n">
+      <c r="V153" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W153" t="inlineStr">
+      <c r="W153" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
+      <c r="X153" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
+      <c r="Y153" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
+      <c r="Z153" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA153" t="inlineStr">
+      <c r="AA153" s="36" t="inlineStr">
         <is>
           <t>16–30</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
+      <c r="AB153" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC153" t="n">
+      <c r="AC153" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD153" t="inlineStr">
+      <c r="AD153" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE153" t="inlineStr">
+      <c r="AE153" s="36" t="inlineStr">
         <is>
           <t>Claudino JG et al. (2018) J Hum Kinet; CrossFit Games official data.</t>
         </is>
       </c>
-      <c r="AF153" t="inlineStr">
+      <c r="AF153" s="36" t="inlineStr">
         <is>
           <t>CrossFit Games female: 165–167 cm, 63–68 kg, high lean mass. Claudino et al. (2018) systematic review.</t>
         </is>
       </c>
-      <c r="AG153" t="inlineStr">
+      <c r="AG153" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="36" t="inlineStr">
         <is>
           <t>SP66F</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="36" t="inlineStr">
         <is>
           <t>Golf</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C154" s="36" t="inlineStr">
         <is>
           <t>Competitive (female)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="36" t="n">
         <v>168</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G154" s="36" t="n">
         <v>73</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H154" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I154" t="n">
+      <c r="I154" s="36" t="n">
         <v>25.9</v>
       </c>
-      <c r="J154" t="n">
+      <c r="J154" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M154" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="N154" t="n">
+      <c r="N154" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="O154" t="n">
+      <c r="O154" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P154" t="n">
+      <c r="P154" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q154" t="n">
+      <c r="Q154" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="R154" t="n">
+      <c r="R154" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="S154" t="n">
+      <c r="S154" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T154" t="n">
+      <c r="T154" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U154" t="n">
+      <c r="U154" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V154" t="n">
+      <c r="V154" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W154" t="inlineStr">
+      <c r="W154" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X154" t="inlineStr">
+      <c r="X154" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
+      <c r="Y154" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
+      <c r="Z154" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA154" t="inlineStr">
+      <c r="AA154" s="36" t="inlineStr">
         <is>
           <t>8–16</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
+      <c r="AB154" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC154" t="n">
+      <c r="AC154" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="AD154" t="inlineStr">
+      <c r="AD154" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE154" t="inlineStr">
+      <c r="AE154" s="36" t="inlineStr">
         <is>
           <t>LPGA Tour athlete data; derived from SP66 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF154" t="inlineStr">
+      <c r="AF154" s="36" t="inlineStr">
         <is>
           <t>LPGA Tour: ~167 cm, 63–67 kg typical. Slightly lighter than simple scaling predicts. Same demands.</t>
         </is>
       </c>
-      <c r="AG154" t="inlineStr">
+      <c r="AG154" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="36" t="inlineStr">
         <is>
           <t>SP68F</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="36" t="inlineStr">
         <is>
           <t>Cricket</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" s="36" t="inlineStr">
         <is>
           <t>All-rounder (female)</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D155" s="36" t="inlineStr">
         <is>
           <t>Team field</t>
         </is>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="36" t="n">
         <v>166</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G155" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H155" t="n">
+      <c r="H155" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I155" t="n">
+      <c r="I155" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="J155" t="n">
+      <c r="J155" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="M155" t="n">
+      <c r="M155" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="N155" t="n">
+      <c r="N155" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="O155" t="n">
+      <c r="O155" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P155" t="n">
+      <c r="P155" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="Q155" t="n">
+      <c r="Q155" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="R155" t="n">
+      <c r="R155" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S155" t="n">
+      <c r="S155" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T155" t="n">
+      <c r="T155" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U155" t="n">
+      <c r="U155" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V155" t="n">
+      <c r="V155" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="W155" t="inlineStr">
+      <c r="W155" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
+      <c r="X155" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
+      <c r="Y155" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
+      <c r="Z155" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr">
+      <c r="AA155" s="36" t="inlineStr">
         <is>
           <t>8–14</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
+      <c r="AB155" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AC155" t="n">
+      <c r="AC155" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD155" t="inlineStr">
+      <c r="AD155" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE155" t="inlineStr">
+      <c r="AE155" s="36" t="inlineStr">
         <is>
           <t>ICC official data; derived from SP68 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF155" t="inlineStr">
+      <c r="AF155" s="36" t="inlineStr">
         <is>
           <t>Women's cricket: shorter/lighter, same technical demands (bowling, batting, fielding). ICC Women's data.</t>
         </is>
       </c>
-      <c r="AG155" t="inlineStr">
+      <c r="AG155" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="36" t="inlineStr">
         <is>
           <t>SP69F</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="36" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C156" s="36" t="inlineStr">
         <is>
           <t>Recurve / compound (female)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="36" t="n">
         <v>161</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G156" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H156" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="I156" t="n">
+      <c r="I156" s="36" t="n">
         <v>23.9</v>
       </c>
-      <c r="J156" t="n">
+      <c r="J156" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="M156" t="n">
+      <c r="M156" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="N156" t="n">
+      <c r="N156" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="O156" t="n">
+      <c r="O156" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="P156" t="n">
+      <c r="P156" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="Q156" t="n">
+      <c r="Q156" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R156" t="n">
+      <c r="R156" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S156" t="n">
+      <c r="S156" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T156" t="n">
+      <c r="T156" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U156" t="n">
+      <c r="U156" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="V156" t="n">
+      <c r="V156" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W156" t="inlineStr">
+      <c r="W156" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X156" t="inlineStr">
+      <c r="X156" s="36" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
+      <c r="Y156" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
+      <c r="Z156" s="36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA156" t="inlineStr">
+      <c r="AA156" s="36" t="inlineStr">
         <is>
           <t>10–16</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
+      <c r="AB156" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC156" t="n">
+      <c r="AC156" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="AD156" t="inlineStr">
+      <c r="AD156" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE156" t="inlineStr">
+      <c r="AE156" s="36" t="inlineStr">
         <is>
           <t>World Archery data; derived from SP69 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF156" t="inlineStr">
+      <c r="AF156" s="36" t="inlineStr">
         <is>
           <t>World Archery women's senior: same technical demand structure. Physical profile lighter.</t>
         </is>
       </c>
-      <c r="AG156" t="inlineStr">
+      <c r="AG156" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="36" t="inlineStr">
         <is>
           <t>SP71F</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="36" t="inlineStr">
         <is>
           <t>Darts</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" s="36" t="inlineStr">
         <is>
           <t>Professional (female)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" s="36" t="inlineStr">
         <is>
           <t>Individual technical</t>
         </is>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="36" t="n">
         <v>161</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="G157" t="n">
+      <c r="G157" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="H157" t="n">
+      <c r="H157" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="I157" t="n">
+      <c r="I157" s="36" t="n">
         <v>26.6</v>
       </c>
-      <c r="J157" t="n">
+      <c r="J157" s="36" t="n">
         <v>28</v>
       </c>
-      <c r="M157" t="n">
+      <c r="M157" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="N157" t="n">
+      <c r="N157" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="O157" t="n">
+      <c r="O157" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="P157" t="n">
+      <c r="P157" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="Q157" t="n">
+      <c r="Q157" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R157" t="n">
+      <c r="R157" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="S157" t="n">
+      <c r="S157" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="T157" t="n">
+      <c r="T157" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U157" t="n">
+      <c r="U157" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="V157" t="n">
+      <c r="V157" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W157" t="inlineStr">
+      <c r="W157" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
+      <c r="X157" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr">
+      <c r="Y157" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
+      <c r="Z157" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA157" t="inlineStr">
+      <c r="AA157" s="36" t="inlineStr">
         <is>
           <t>14–30</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
+      <c r="AB157" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC157" t="n">
+      <c r="AC157" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="AD157" t="inlineStr">
+      <c r="AD157" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE157" t="inlineStr">
+      <c r="AE157" s="36" t="inlineStr">
         <is>
           <t>PDC Women's Series data; derived from SP71 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF157" t="inlineStr">
+      <c r="AF157" s="36" t="inlineStr">
         <is>
           <t>Women's darts: similar physical profile to male (non-athletic sport). BDO / PDC women's tour.</t>
         </is>
       </c>
-      <c r="AG157" t="inlineStr">
+      <c r="AG157" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="36" t="inlineStr">
         <is>
           <t>SP72F</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="36" t="inlineStr">
         <is>
           <t>Lawn bowls</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="36" t="inlineStr">
         <is>
           <t>Competitive (female)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" s="36" t="inlineStr">
         <is>
           <t>Team precision</t>
         </is>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="36" t="n">
         <v>161</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G158" t="n">
+      <c r="G158" s="36" t="n">
         <v>67</v>
       </c>
-      <c r="H158" t="n">
+      <c r="H158" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="I158" t="n">
+      <c r="I158" s="36" t="n">
         <v>25.8</v>
       </c>
-      <c r="J158" t="n">
+      <c r="J158" s="36" t="n">
         <v>27</v>
       </c>
-      <c r="M158" t="n">
+      <c r="M158" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="N158" t="n">
+      <c r="N158" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="O158" t="n">
+      <c r="O158" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="P158" t="n">
+      <c r="P158" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="Q158" t="n">
+      <c r="Q158" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R158" t="n">
+      <c r="R158" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="S158" t="n">
+      <c r="S158" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="T158" t="n">
+      <c r="T158" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U158" t="n">
+      <c r="U158" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="V158" t="n">
+      <c r="V158" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="W158" t="inlineStr">
+      <c r="W158" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
+      <c r="X158" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="Y158" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
+      <c r="Z158" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr">
+      <c r="AA158" s="36" t="inlineStr">
         <is>
           <t>16+</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
+      <c r="AB158" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC158" t="n">
+      <c r="AC158" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD158" t="inlineStr">
+      <c r="AD158" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE158" t="inlineStr">
+      <c r="AE158" s="36" t="inlineStr">
         <is>
           <t>World Bowls data; derived from SP72 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF158" t="inlineStr">
+      <c r="AF158" s="36" t="inlineStr">
         <is>
           <t>Women's lawn bowls: similar demands and profile. Bowls NZ / Bowls England women's competitions.</t>
         </is>
       </c>
-      <c r="AG158" t="inlineStr">
+      <c r="AG158" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="36" t="inlineStr">
         <is>
           <t>SP74F</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="36" t="inlineStr">
         <is>
           <t>Karate</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="36" t="inlineStr">
         <is>
           <t>Kumite (female elite)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" s="36" t="inlineStr">
         <is>
           <t>Combat striking</t>
         </is>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="36" t="n">
         <v>161</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G159" t="n">
+      <c r="G159" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="H159" t="n">
+      <c r="H159" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I159" t="n">
+      <c r="I159" s="36" t="n">
         <v>23.9</v>
       </c>
-      <c r="J159" t="n">
+      <c r="J159" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M159" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="N159" t="n">
+      <c r="N159" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O159" t="n">
+      <c r="O159" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P159" t="n">
+      <c r="P159" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q159" t="n">
+      <c r="Q159" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="R159" t="n">
+      <c r="R159" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="S159" t="n">
+      <c r="S159" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="T159" t="n">
+      <c r="T159" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="U159" t="n">
+      <c r="U159" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="V159" t="n">
+      <c r="V159" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W159" t="inlineStr">
+      <c r="W159" s="36" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
+      <c r="X159" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
+      <c r="Y159" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
+      <c r="Z159" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA159" t="inlineStr">
+      <c r="AA159" s="36" t="inlineStr">
         <is>
           <t>6–12</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
+      <c r="AB159" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AC159" t="n">
+      <c r="AC159" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="AD159" t="inlineStr">
+      <c r="AD159" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE159" t="inlineStr">
+      <c r="AE159" s="36" t="inlineStr">
         <is>
           <t>World Karate Federation data; derived from SP74 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF159" t="inlineStr">
+      <c r="AF159" s="36" t="inlineStr">
         <is>
           <t>WKF women's kumite: lighter, shorter than male. Same speed-reaction-technique demand profile.</t>
         </is>
       </c>
-      <c r="AG159" t="inlineStr">
+      <c r="AG159" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="36" t="inlineStr">
         <is>
           <t>SP75F</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="36" t="inlineStr">
         <is>
           <t>Muay Thai</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C160" s="36" t="inlineStr">
         <is>
           <t>Professional (light–flyweight, female)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" s="36" t="inlineStr">
         <is>
           <t>Combat striking</t>
         </is>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="36" t="n">
         <v>158</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="G160" t="n">
+      <c r="G160" s="36" t="n">
         <v>57</v>
       </c>
-      <c r="H160" t="n">
+      <c r="H160" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I160" t="n">
+      <c r="I160" s="36" t="n">
         <v>22.8</v>
       </c>
-      <c r="J160" t="n">
+      <c r="J160" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="M160" t="n">
+      <c r="M160" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="N160" t="n">
+      <c r="N160" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="O160" t="n">
+      <c r="O160" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="P160" t="n">
+      <c r="P160" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="Q160" t="n">
+      <c r="Q160" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="R160" t="n">
+      <c r="R160" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="S160" t="n">
+      <c r="S160" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="T160" t="n">
+      <c r="T160" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="U160" t="n">
+      <c r="U160" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="V160" t="n">
+      <c r="V160" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="W160" t="inlineStr">
+      <c r="W160" s="36" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
+      <c r="X160" s="36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
+      <c r="Y160" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
+      <c r="Z160" s="36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AA160" t="inlineStr">
+      <c r="AA160" s="36" t="inlineStr">
         <is>
           <t>10–18</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
+      <c r="AB160" s="36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC160" t="n">
+      <c r="AC160" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AD160" t="inlineStr">
+      <c r="AD160" s="36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE160" t="inlineStr">
+      <c r="AE160" s="36" t="inlineStr">
         <is>
           <t>WBKF / IFMA data; derived from SP75 via sex differentials.</t>
         </is>
       </c>
-      <c r="AF160" t="inlineStr">
+      <c r="AF160" s="36" t="inlineStr">
         <is>
           <t>Female Muay Thai pros: lighter weight classes dominate. Same striking-dominant demand profile.</t>
         </is>
       </c>
-      <c r="AG160" t="inlineStr">
+      <c r="AG160" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
